--- a/InputFiles/ICDC/TC30_Canine_Study-PRECINCT01-FileType-SupplDataFile.xlsx
+++ b/InputFiles/ICDC/TC30_Canine_Study-PRECINCT01-FileType-SupplDataFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\ICDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA248F7E-F32B-493D-ADCC-05CCD23D8979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31F1DC4-0FC4-47BF-95E2-236CE804DB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31020" yWindow="2220" windowWidth="21600" windowHeight="11265" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="startup" sheetId="1" r:id="rId1"/>
@@ -64,50 +64,6 @@
   </si>
   <si>
     <t>TC30_Canine_Study-PRECINCT01-FileType-SupplDataFile_WebData.xlsx</t>
-  </si>
-  <si>
-    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic)
-MATCH (c)&lt;--(diag:diagnosis)
-Where s.clinical_study_designation IN ['PRECINCT01']
-  MATCH (f:file)-[*]-&gt;(c)
-   WHERE f.file_type IN ["Supplemental Data File"] 
-OPTIONAL MATCH (co:cohort)&lt;-[*]-(c)
-  WITH DISTINCT c, s, demo, diag, co,demo.patient_age_at_enrollment AS age, demo.weight as weight
-RETURN  coalesce(c.case_id, '') AS `Case ID` ,
-        coalesce(s.clinical_study_designation, '') AS `Study Code` ,
-        coalesce(s.clinical_study_type, '') AS  `Study Type`,
-        coalesce(demo.breed, '') AS Breed ,
-        coalesce(diag.disease_term, '') AS Diagnosis ,
-        coalesce(diag.stage_of_disease, '') AS `Stage of Disease` ,
-  coalesce(CASE age % 1 WHEN 0 THEN apoc.convert.toInteger(age) ELSE age END, '') AS Age,
-       coalesce(demo.sex, '') AS Sex,
-       coalesce(demo.neutered_indicator, '') AS `Neutered Status`,
-coalesce(CASE weight % 1 WHEN 0 THEN apoc.convert.toInteger(weight) ELSE weight END, '') AS `Weight (kg)`,
-       coalesce(diag.best_response, '') AS `Response to Treatment`,
-       coalesce(co.cohort_description, '') AS `Cohort`
-order by c.case_id asc
-limit 100</t>
-  </si>
-  <si>
-    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
-Where s.clinical_study_designation IN ['PRECINCT01']
-MATCH (f:file)-[*]-&gt;(c)
-WHERE f.file_type IN ["Supplemental Data File"]  
-WITH DISTINCT samp AS samp, c, demo, diag
-RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
-        coalesce(c.case_id, '') AS `Case ID`, 
-        coalesce(demo.breed,'') AS Breed,
-        coalesce(diag.disease_term,'') AS Diagnosis, 
-        coalesce(samp.sample_site, '') AS `Sample Site`,
-        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
-        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
-        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
-        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
-        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
-        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
-        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
-order by samp.sample_id asc
-limit 100</t>
   </si>
   <si>
     <t>MATCH (f:file)--&gt;(parent)
@@ -189,6 +145,50 @@
     count(distinct samp) AS Samples,
     count(distinct f) AS `Case Files`,
     count(distinct sf) AS `Study Files`</t>
+  </si>
+  <si>
+    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic)
+MATCH (c)&lt;--(diag:diagnosis)
+Where s.clinical_study_designation IN ['PRECINCT01']
+  MATCH (f:file)-[*]-&gt;(s)
+   WHERE f.file_type IN ["Supplemental Data File"] 
+OPTIONAL MATCH (co:cohort)&lt;-[*]-(c)
+  WITH DISTINCT c, s, demo, diag, co,demo.patient_age_at_enrollment AS age, demo.weight as weight
+RETURN  coalesce(c.case_id, '') AS `Case ID` ,
+        coalesce(s.clinical_study_designation, '') AS `Study Code` ,
+        coalesce(s.clinical_study_type, '') AS  `Study Type`,
+        coalesce(demo.breed, '') AS Breed ,
+        coalesce(diag.disease_term, '') AS Diagnosis ,
+        coalesce(diag.stage_of_disease, '') AS `Stage of Disease` ,
+  coalesce(CASE age % 1 WHEN 0 THEN apoc.convert.toInteger(age) ELSE age END, '') AS Age,
+       coalesce(demo.sex, '') AS Sex,
+       coalesce(demo.neutered_indicator, '') AS `Neutered Status`,
+coalesce(CASE weight % 1 WHEN 0 THEN apoc.convert.toInteger(weight) ELSE weight END, '') AS `Weight (kg)`,
+       coalesce(diag.best_response, '') AS `Response to Treatment`,
+       coalesce(co.cohort_description, '') AS `Cohort`
+order by c.case_id asc
+limit 100</t>
+  </si>
+  <si>
+    <t>MATCH (s:study)&lt;-[*]-(c:case)&lt;--(demo:demographic), (samp:sample)--&gt;(c)&lt;--(diag:diagnosis) 
+MATCH (r:registration)--&gt;(c)
+MATCH (f:file)-[*]-&gt;(s)
+WHERE s.clinical_study_designation IN ['PRECINCT01'] and f.file_type in ['Supplemental Data File']
+WITH DISTINCT samp AS samp, c, demo, diag
+RETURN  coalesce(samp.sample_id, '') AS `Sample ID`, 
+        coalesce(c.case_id, '') AS `Case ID`, 
+        coalesce(demo.breed,'') AS Breed,
+        coalesce(diag.disease_term,'') AS Diagnosis, 
+        coalesce(samp.sample_site, '') AS `Sample Site`,
+        coalesce(samp.summarized_sample_type, '') AS `Sample Type`,
+        coalesce(samp.specific_sample_pathology, '') AS `Pathology/Morphology`,
+        coalesce(samp.tumor_grade, '') AS `Tumor Grade`,
+        coalesce(samp.sample_chronology, '') AS `Sample Chronology`,
+        coalesce(samp.percentage_tumor, '') AS `Percentage Tumor`,
+        coalesce(samp.necropsy_sample, '') AS `Necropsy Sample`,
+        coalesce(samp.sample_preservation, '') AS `Sample Preservation`
+order by samp.sample_id asc
+limit 100</t>
   </si>
 </sst>
 </file>
@@ -262,9 +262,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -302,7 +302,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -408,7 +408,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -550,7 +550,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -591,10 +591,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>9</v>
@@ -608,10 +608,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
@@ -625,10 +625,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>9</v>
@@ -642,10 +642,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
